--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,10 +84,12 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Libellé court de l'organisation
++The Organization short name</t>
+  </si>
+  <si>
     <t>Purpose</t>
-  </si>
-  <si>
-    <t>The Organization short name | Libellé court de l'organisation</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -259,9 +261,6 @@
 </t>
   </si>
   <si>
-    <t>An Extension</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -297,6 +296,9 @@
   <si>
     <t xml:space="preserve">Extension
 </t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -580,15 +582,15 @@
       <c r="A13" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>24</v>
       </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -847,7 +849,7 @@
         <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -907,10 +909,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>77</v>
@@ -918,10 +920,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -932,25 +934,25 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1001,13 +1003,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1016,15 +1018,15 @@
         <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1047,13 +1049,13 @@
         <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1116,7 +1118,7 @@
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1135,10 +1137,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
@@ -1212,10 +1214,10 @@
         <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
@@ -1243,19 +1245,19 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>104</v>
@@ -1318,7 +1320,7 @@
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-short-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
